--- a/명단.xlsx
+++ b/명단.xlsx
@@ -1,40 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JB_Agent\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5BC9FE-60EE-401F-88EF-53566735F49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B5158D77-17E6-4B1B-9410-ED1097E4F98B}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -42,95 +14,73 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>김광녕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>김형정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>김홍석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>남광봉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>박명식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>설동민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>원상호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>유정욱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>이병동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>이홍범</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>임정빈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>정성영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>정현철</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>조관진</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>최주용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>한승엽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>홍성화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>이명주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -139,207 +89,89 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
+  <borders count="1">
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -401,6 +233,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -409,13 +248,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -480,133 +312,107 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F871A23-131B-4416-87DD-0B05FB365B77}">
-  <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="5">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="6">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="7">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="8">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="9">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="10">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="11">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="12">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="13">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="14">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="15">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="16">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="17">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="18">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>